--- a/results/Int All Data 0.3/Rando_3_permute.xlsx
+++ b/results/Int All Data 0.3/Rando_3_permute.xlsx
@@ -440,1547 +440,1547 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8499073699201144</v>
+        <v>0.862192670566162</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8473805221626918</v>
+        <v>0.8618768145964841</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8411461081976046</v>
+        <v>0.870753863918851</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8314869018231428</v>
+        <v>0.8738793414442416</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8343047939217023</v>
+        <v>0.8700973403509547</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8352523618307359</v>
+        <v>0.8654587473199502</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8365157857094472</v>
+        <v>0.8708282988044733</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8309875185693378</v>
+        <v>0.8680186772487606</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8290510300370363</v>
+        <v>0.8685924953881878</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8281117326708498</v>
+        <v>0.8674035063950988</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8548933257506897</v>
+        <v>0.8736710025315737</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8568050026544505</v>
+        <v>0.8802957073519613</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8423583334777396</v>
+        <v>0.8790157423875561</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8442617398386536</v>
+        <v>0.8780929861070633</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8514437217127744</v>
+        <v>0.8831135994505208</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8521002452806707</v>
+        <v>0.8790322834732499</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8615841949138525</v>
+        <v>0.8815260490592848</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8593897442118015</v>
+        <v>0.8746268409834541</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8634876012747663</v>
+        <v>0.8740033995869454</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8636876696445872</v>
+        <v>0.8865549329455893</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8636876696445872</v>
+        <v>0.886879059458114</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8608697775460276</v>
+        <v>0.8812019225467601</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8594145558403423</v>
+        <v>0.8858405155777644</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8568877080829197</v>
+        <v>0.8808447138628477</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8556160136613614</v>
+        <v>0.8833550205345764</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.840322598431275</v>
+        <v>0.8833550205345764</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8599056685513002</v>
+        <v>0.8646864361521969</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8386176850986873</v>
+        <v>0.8668808868542478</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8555167671471984</v>
+        <v>0.872242167795924</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8605539215763498</v>
+        <v>0.872242167795924</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8652586789501294</v>
+        <v>0.870347031977857</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8661897057734691</v>
+        <v>0.8526425565902048</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8655579938341134</v>
+        <v>0.8529253303884949</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.846282509140919</v>
+        <v>0.854704678606705</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8447032292925298</v>
+        <v>0.8588025356696698</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8468480567374993</v>
+        <v>0.856890858765909</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8465239302249745</v>
+        <v>0.8566080849676189</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8167988115623764</v>
+        <v>0.8603404628038243</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8233573520399884</v>
+        <v>0.8211825931066207</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8073975673576639</v>
+        <v>0.8224129348139443</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8175726980716245</v>
+        <v>0.8158378532506384</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8138734024068067</v>
+        <v>0.8187136391491265</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.822302267073945</v>
+        <v>0.8161454386774694</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8154278706266551</v>
+        <v>0.8058048971065703</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8157602676820268</v>
+        <v>0.8076752212960965</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8214622162219215</v>
+        <v>0.7943182945983116</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8158843258247306</v>
+        <v>0.7889239314852476</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8074058379005109</v>
+        <v>0.7844936773669112</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.795492711682575</v>
+        <v>0.7838867770560963</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.824113122122048</v>
+        <v>0.7936948532018029</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8243628137489505</v>
+        <v>0.7990147814292443</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8246455875472405</v>
+        <v>0.8099704938538052</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8252690289437493</v>
+        <v>0.801118256159979</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8031906178961945</v>
+        <v>0.7964217693290463</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8100071205435557</v>
+        <v>0.7964217693290463</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8584933749013443</v>
+        <v>0.7556515376120658</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8588009603281752</v>
+        <v>0.7780855820020385</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8713938464010536</v>
+        <v>0.7834468629437146</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.872473742995638</v>
+        <v>0.786006792872525</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8797632419267687</v>
+        <v>0.8151068947971196</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8927133366835596</v>
+        <v>0.7933459150607373</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8857479642649535</v>
+        <v>0.7908273378461617</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8891065923315526</v>
+        <v>0.7908273378461617</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8891065923315526</v>
+        <v>0.7841860919400803</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.8859299162075859</v>
+        <v>0.7886246166012638</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8760970284333387</v>
+        <v>0.7864053542706719</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8554738390914691</v>
+        <v>0.7807199468164712</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8481926107031852</v>
+        <v>0.7648279018184168</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8558475888610753</v>
+        <v>0.7471234264307645</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.8629551358495737</v>
+        <v>0.7300672040681618</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8190314642956726</v>
+        <v>0.7316464839165511</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8307264057165993</v>
+        <v>0.7338574757042958</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.829454711295041</v>
+        <v>0.7484282030237104</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8300781526915497</v>
+        <v>0.7364339467187999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.8114922737376394</v>
+        <v>0.7241321049870586</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.8226480545320212</v>
+        <v>0.7244479609567364</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7937696819227988</v>
+        <v>0.7225445545958226</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7563549275894281</v>
+        <v>0.669431128432866</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.756670783559106</v>
+        <v>0.633099421377069</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7639634331732261</v>
+        <v>0.6849576942041611</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7704806209366035</v>
+        <v>0.6804530052002022</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7826418634399472</v>
+        <v>0.7098193398373933</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7841715200312547</v>
+        <v>0.7053890857190568</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7742460809441967</v>
+        <v>0.706652509597768</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7704309976795219</v>
+        <v>0.706652509597768</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.771735774272468</v>
+        <v>0.6968842108248016</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7676115302394677</v>
+        <v>0.696543543226583</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7813437820483535</v>
+        <v>0.6975490049355448</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.7766803773888085</v>
+        <v>0.6957546909731357</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.7766803773888085</v>
+        <v>0.7317374598878672</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7952000919999433</v>
+        <v>0.7524748614880992</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7667880204731381</v>
+        <v>0.7624830060036265</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.7604362435666991</v>
+        <v>0.7554266576137042</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.7406432591925114</v>
+        <v>0.7706125557867807</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.7540513844888725</v>
+        <v>0.7683188585705667</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.7520983548708771</v>
+        <v>0.7359857620635714</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.7527548784387735</v>
+        <v>0.7185723310170562</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.7321647712682917</v>
+        <v>0.7204674668351232</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.7321647712682917</v>
+        <v>0.6696146557169931</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.7559563661912811</v>
+        <v>0.6228679722046747</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.7357151971618647</v>
+        <v>0.6156032849020846</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.7635302142621967</v>
+        <v>0.6250789639924195</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.7700722136541149</v>
+        <v>0.591282375236892</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.6087678781567875</v>
+        <v>0.6036007580543272</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.6074217488496069</v>
+        <v>0.5960202147820594</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.6006532941178324</v>
+        <v>0.5960202147820594</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.6006532941178324</v>
+        <v>0.605811749842072</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.6062808077721048</v>
+        <v>0.605811749842072</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5934098739254201</v>
+        <v>0.6073910296904611</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.586652840419482</v>
+        <v>0.6365076727007497</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.6028623167287088</v>
+        <v>0.6254527137620258</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.6028623167287088</v>
+        <v>0.6245051458529923</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.6075339919311009</v>
+        <v>0.6102916272174901</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5815924497032845</v>
+        <v>0.6100253945048938</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5713113772738085</v>
+        <v>0.6119370714086546</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.555574897248351</v>
+        <v>0.6068337526367278</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5439476955116945</v>
+        <v>0.6182045675451295</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5503392497908735</v>
+        <v>0.6182045675451295</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5968905909578549</v>
+        <v>0.6027358955737629</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5931649083230017</v>
+        <v>0.6027358955737629</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5739855194609811</v>
+        <v>0.5824797608001474</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5728823865793506</v>
+        <v>0.6036669223971026</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5434762745694198</v>
+        <v>0.6292760675695475</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5099242575809371</v>
+        <v>0.6292760675695475</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4830036406141942</v>
+        <v>0.6254857959334135</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.488210931924768</v>
+        <v>0.6174141399501877</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4960080846525506</v>
+        <v>0.6113715238120744</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4956922286828728</v>
+        <v>0.5964849405229818</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4956922286828728</v>
+        <v>0.5964849405229818</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4953763727131949</v>
+        <v>0.5955291020711015</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5026576011014787</v>
+        <v>0.5892367943060857</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5029734570711566</v>
+        <v>0.5716878838910304</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5029734570711566</v>
+        <v>0.5484649872476106</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5042286104070209</v>
+        <v>0.5530771933085794</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4942039248057998</v>
+        <v>0.5480234977937342</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5019514542765008</v>
+        <v>0.5466939095722475</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5019514542765008</v>
+        <v>0.5601433875828432</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5043707849769133</v>
+        <v>0.5329136098477748</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5046783704037443</v>
+        <v>0.5247178957218451</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5030908200125082</v>
+        <v>0.5113030752241317</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.501220495822982</v>
+        <v>0.5084438304113374</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4952026913134095</v>
+        <v>0.5072052181611669</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4942220412329883</v>
+        <v>0.5072052181611669</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5012882355072521</v>
+        <v>0.5014453758213437</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5006647941107434</v>
+        <v>0.5075045330451509</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5013047765929459</v>
+        <v>0.5085182652969598</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5013047765929459</v>
+        <v>0.5021018993892401</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5000413527142347</v>
+        <v>0.5048784387735652</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5006317119393556</v>
+        <v>0.5035653916377723</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5000082705428469</v>
+        <v>0.5045129595468058</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5000082705428469</v>
+        <v>0.5045129595468058</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5003241265125248</v>
+        <v>0.4960923654225144</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5000082705428469</v>
+        <v>0.4957186156529082</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4993848291463382</v>
+        <v>0.4950786331707056</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4981462168961677</v>
+        <v>0.4963420570494169</v>
       </c>
     </row>
   </sheetData>
